--- a/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Alloggi sociali.xlsx
+++ b/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Alloggi sociali.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="149">
   <si>
     <r>
       <t xml:space="preserve">
@@ -554,7 +554,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t>[Solo per messaggi Premium con allegato]</t>
+      <t>[Solo per messaggi con allegato]</t>
     </r>
     <r>
       <rPr>
@@ -1152,7 +1152,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t>[Solo per messaggi Premium con allegato]</t>
+      <t>[Solo per messaggi con allegato]</t>
     </r>
     <r>
       <rPr>
@@ -1338,141 +1338,6 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve">C'è un avviso da pagare intestato a </t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="ff884444"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t>&lt;nome&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="ff884444"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t>&lt;cognome&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t xml:space="preserve"> e relativo a </t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="ff884444"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t>&lt;causale&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t xml:space="preserve">.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t>Devi pagare:</t>
-    </r>
-    <r>
-      <rPr>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="ff884444"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t>&lt;00,00&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t xml:space="preserve"> €
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t>Entro il:</t>
-    </r>
-    <r>
-      <rPr>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="ff884444"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t>&lt;gg/mm/aaaa&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t xml:space="preserve">
-Puoi pagare direttamente in app premendo “Vedi Avviso”, oppure tramite tutti i canali di Puoi pagare direttamente in app premendo “Paga”, oppure tramite tutti i canali di pagamento della piattaforma pagoPA e le altre modalità di pagamento offerte dell'ente creditore.
-Se hai già provveduto a pagare l'avviso, ignora questo messaggio.
-Per maggiori informazioni o per richiedere assistenza, contattaci tramite i canali che trovi nella scheda servizio.
-In fase di pagamento, se previsto dall'ente, l'importo riportato nel messaggio potrebbe subire variazioni.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
       <t xml:space="preserve">Il tuo pagamento relativo a </t>
     </r>
     <r>
@@ -1525,13 +1390,16 @@
     </r>
   </si>
   <si>
-    <t>-</t>
+    <t>Vai ai bandi aperti</t>
   </si>
   <si>
     <t>Disdici appuntamento</t>
   </si>
   <si>
     <t>Paga (inserito automaticamente dall'app se il messaggio prevede un avviso di pagamento pagoPA)</t>
+  </si>
+  <si>
+    <t>Consulta la pratica</t>
   </si>
   <si>
     <t>Accedi al portale</t>
@@ -1543,7 +1411,7 @@
     <t>Vai alla graduatoria</t>
   </si>
   <si>
-    <t>Vai ala graduatoria</t>
+    <t>-</t>
   </si>
   <si>
     <r>
@@ -1563,7 +1431,7 @@
       <rPr>
         <b/>
       </rPr>
-      <t>Allegato (Premium)</t>
+      <t>Allegato</t>
     </r>
     <r>
       <rPr/>
@@ -1688,28 +1556,6 @@
       </rPr>
       <t>Note aggiuntive</t>
     </r>
-  </si>
-  <si>
-    <t xml:space="preserve">✨ Allegati Premium — Tramite questa funzionalità Premium, disponibile a seconda della tipologia di contratto sottoscritto dall’ente, puoi allegare documenti all'interno del messaggio.
-Questo messaggio è da utilizzare sia per messaggi Premium, sia per messaggi standard. In caso di messaggio standard, ricorda di eliminare ogni riferimento agli allegati dal corpo del messaggio.</t>
-  </si>
-  <si>
-    <t>✨Messaggio Premium — Se hai un contratto Premium, ti consigliamo di configurare questo messaggio con promemoria Premium: i destinatari verranno avvisati dell‘avvicinarsi dell'appuntamento tramite notifica push.</t>
-  </si>
-  <si>
-    <t>✨ Messaggio Premium — Se hai un contratto Premium, ti consigliamo di configurare questo messaggio con promemoria Premium: i destinatari verranno avvisati dell‘avvicinarsi della scadenza tramite notifica push.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Promemoria automatici — Messaggi Premium
-Impostando il messaggio di Avviso di pagamento come Messaggio Premium, disponibile a seconda della tipologia di contratto sottoscritto dall’ente, non è necessario inviare il seguente messaggio di promemoria.
-Gli utenti che hanno dato il loro consenso, infatti, riceveranno automaticamente una notifica push sui loro dispositivi all’avvicinarsi della scadenza.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Firma con IO
-Tramite la funzionalità Firma con IO puoi inviare al destinatario il documento da firmare e permettere la firma direttamente in app. Scopri di più (https://firma.io.italia.it/)
-Il seguente messaggio è da utilizzare nei casi di altre modalità di firma e non è necessario quando si utilizza Firma con IO.
-✨ Allegati Premium — Tramite questa funzionalità Premium, disponibile a seconda della tipologia di contratto sottoscritto dall’ente, puoi allegare documenti all'interno del messaggio.
-Questo messaggio è da utilizzare sia per messaggi Premium, sia per messaggi standard. In caso di messaggio standard, ricorda di eliminare ogni riferimento agli allegati dal corpo del messaggio.</t>
   </si>
   <si>
     <t xml:space="preserve">Mancato pagamento
@@ -2523,33 +2369,33 @@
         <v>104</v>
       </c>
       <c r="N5" s="34" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="O5" s="34" t="s">
         <v>96</v>
       </c>
       <c r="P5" s="34" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="32" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" s="32" t="s">
+      <c r="B6" s="34" t="s">
         <v>107</v>
       </c>
-      <c r="B6" s="34" t="s">
+      <c r="C6" s="34" t="s">
         <v>108</v>
       </c>
-      <c r="C6" s="34" t="s">
+      <c r="D6" s="34" t="s">
         <v>109</v>
       </c>
-      <c r="D6" s="34" t="s">
-        <v>110</v>
-      </c>
       <c r="E6" s="34" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F6" s="34" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="G6" s="34" t="s">
         <v>111</v>
@@ -2561,25 +2407,25 @@
         <v>113</v>
       </c>
       <c r="J6" s="34" t="s">
+        <v>113</v>
+      </c>
+      <c r="K6" s="34" t="s">
         <v>114</v>
       </c>
-      <c r="K6" s="34" t="s">
+      <c r="L6" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="M6" s="34" t="s">
         <v>108</v>
       </c>
-      <c r="L6" s="34" t="s">
-        <v>108</v>
-      </c>
-      <c r="M6" s="34" t="s">
+      <c r="N6" s="34" t="s">
         <v>109</v>
       </c>
-      <c r="N6" s="34" t="s">
-        <v>110</v>
-      </c>
       <c r="O6" s="34" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="P6" s="34" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
@@ -2640,46 +2486,46 @@
         <v>117</v>
       </c>
       <c r="C8" s="34" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="D8" s="34" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="E8" s="34" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="F8" s="34" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="G8" s="34" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="H8" s="34" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="I8" s="34" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="J8" s="34" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="K8" s="34" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="L8" s="34" t="s">
         <v>118</v>
       </c>
       <c r="M8" s="34" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="N8" s="34" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="O8" s="34" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="P8" s="34" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
@@ -2787,16 +2633,16 @@
         <v>147</v>
       </c>
       <c r="B11" s="34" t="s">
-        <v>148</v>
+        <v>64</v>
       </c>
       <c r="C11" s="34" t="s">
-        <v>149</v>
+        <v>64</v>
       </c>
       <c r="D11" s="34" t="s">
-        <v>150</v>
+        <v>64</v>
       </c>
       <c r="E11" s="34" t="s">
-        <v>151</v>
+        <v>64</v>
       </c>
       <c r="F11" s="34" t="s">
         <v>64</v>
@@ -2817,19 +2663,19 @@
         <v>64</v>
       </c>
       <c r="L11" s="34" t="s">
-        <v>152</v>
+        <v>64</v>
       </c>
       <c r="M11" s="34" t="s">
-        <v>149</v>
+        <v>64</v>
       </c>
       <c r="N11" s="34" t="s">
-        <v>150</v>
+        <v>64</v>
       </c>
       <c r="O11" s="34" t="s">
-        <v>151</v>
+        <v>64</v>
       </c>
       <c r="P11" s="34" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
     </row>
   </sheetData>
